--- a/documentacao/Testes/Caso de Teste/UC19 - DISPONIBILIZAR CONSULTAS .xlsx
+++ b/documentacao/Testes/Caso de Teste/UC19 - DISPONIBILIZAR CONSULTAS .xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="84">
   <si>
     <t xml:space="preserve">Caso de Teste</t>
   </si>
@@ -43,6 +43,9 @@
     <t xml:space="preserve">Observações</t>
   </si>
   <si>
+    <t xml:space="preserve">Status de teste v2 (OK/NOK)</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -52,14 +55,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT – 01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Cadastro bem-sucedido de disponibilidade</t>
     </r>
@@ -103,14 +107,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Período superior a 90 dias</t>
     </r>
@@ -142,6 +147,9 @@
     <t xml:space="preserve">Nenhum tipo de mensagem é exibida</t>
   </si>
   <si>
+    <t xml:space="preserve">Nenhum tipo de mensagem é exibida e sistema salva normalmente.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -151,14 +159,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 03 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Data final anterior à data inicial</t>
     </r>
@@ -194,14 +203,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 04 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Horário fim anterior ao início</t>
     </r>
@@ -234,14 +244,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 05 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Jornada superior a 12 horas</t>
     </r>
@@ -275,14 +286,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Duração mínima inferior a 15min</t>
     </r>
@@ -313,14 +325,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Duração superior a 240min</t>
     </r>
@@ -348,14 +361,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 08 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Intervalo inferior a 5min</t>
     </r>
@@ -383,14 +397,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 09 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Preço negativo</t>
     </r>
@@ -418,14 +433,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Nenhum dia selecionado</t>
     </r>
@@ -453,14 +469,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Conflito com horários existentes</t>
     </r>
@@ -493,14 +510,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Limite de 40 horários por dia</t>
     </r>
@@ -533,14 +551,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 13 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Antecedência mínima de 24h</t>
     </r>
@@ -570,14 +589,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 14 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Cancelamento do processo</t>
     </r>
@@ -608,14 +628,15 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CT- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
+      <t xml:space="preserve">CT- 15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Múltiplas clínicas vinculadas</t>
     </r>
@@ -647,7 +668,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -701,6 +722,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF404040"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -749,7 +776,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -758,7 +785,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -766,15 +797,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -782,19 +817,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -981,382 +1028,467 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="37.33"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1023" min="4" style="1" width="32.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="2" width="11.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="129.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="126.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="F2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="G2" s="9"/>
+      <c r="H2" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="F3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="H3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="5" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="E4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="F4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="H4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="E5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="F5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="H5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="B6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="43.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="E6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="F6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="H6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="B7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="43.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="E7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="F7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="H7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="B8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="43.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="F8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="B9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="43.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="F9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="B10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="43.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="E10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="F10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="B11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="8"/>
-    </row>
-    <row r="12" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="E11" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="F11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="56.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="F12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="56.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="C13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="58" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="E13" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="F13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="56.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="B14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="43.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="E14" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="F14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="B15" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="C15" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="43.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="E15" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="F15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="B16" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="C16" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>12</v>
+      <c r="D16" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="10"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="15"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
